--- a/lab3/mixer-oscillator/calculator.xlsx
+++ b/lab3/mixer-oscillator/calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab3\mixer-oscillator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0894388A-D586-4EAF-B11F-6A7E13BBACB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{543B40AF-891B-491D-A4A4-6E8AE20A8D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8736" yWindow="696" windowWidth="13740" windowHeight="11232" xr2:uid="{A50CB518-3203-47F3-A69B-33C5CFC9F0B6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t>f (MHz)</t>
   </si>
@@ -65,6 +65,9 @@
     <t>L(nH)</t>
   </si>
   <si>
+    <t>C (nF)</t>
+  </si>
+  <si>
     <t>Q</t>
   </si>
   <si>
@@ -74,16 +77,7 @@
     <t>&gt;=18</t>
   </si>
   <si>
-    <t>C (F)</t>
-  </si>
-  <si>
-    <t>BW</t>
-  </si>
-  <si>
-    <t>L (H)</t>
-  </si>
-  <si>
-    <t>f0 (Hz)</t>
+    <t>10n for 18pF</t>
   </si>
 </sst>
 </file>
@@ -91,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -122,9 +116,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A9D7642-A24D-49E2-BA76-F7C73C4022A4}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -489,14 +484,14 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
       </c>
       <c r="F2">
         <f>B2</f>
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -505,14 +500,14 @@
       </c>
       <c r="B3" s="1">
         <f>1/((2*PI()*B1*10^6)^2*B2*10^(-9))*10^12</f>
-        <v>43.957892389602328</v>
+        <v>52.749470867522795</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="1">
         <f>1/((2*PI()*F1*10^6)^2*F2*10^(-9))*10^12</f>
-        <v>29.317472118731988</v>
+        <v>35.180966542478394</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -520,29 +515,29 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>2</v>
       </c>
       <c r="F4">
         <f>B4</f>
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>10</v>
+      <c r="B5" s="2">
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <f>B5</f>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -551,20 +546,20 @@
       </c>
       <c r="B6" s="1">
         <f>B3-B5*B4/(B5+B4)</f>
-        <v>34.866983298693235</v>
+        <v>35.826393944445869</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="1">
         <f>F3-F5*F4/(F5+F4)</f>
-        <v>20.226563027822898</v>
+        <v>18.257889619401471</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -592,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>445</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -612,7 +607,7 @@
         <v>6</v>
       </c>
       <c r="B10">
-        <v>50</v>
+        <v>2200</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -631,91 +626,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1">
-        <f>1/((2*PI()*B8*10^6)^2*B9*10^(-9))*10^12</f>
-        <v>497.17890891966317</v>
-      </c>
-      <c r="C12" s="2"/>
+        <f>1/((2*PI()*B8*10^6)^2*B9*10^(-9))*10^9</f>
+        <v>2.2124461446925014</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3">
         <f>B10*SQRT(B12*10^(-9)/(B9*10^(-9)))</f>
-        <v>52.850164973734159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="2">
-        <f>B12*3/2</f>
-        <v>745.76836337949476</v>
+        <v>327.23446243193439</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="2">
-        <f>B14*2</f>
-        <v>1491.5367267589895</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
         <v>13</v>
-      </c>
-      <c r="B19">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20">
-        <f>1/(B18*B19*2*PI())</f>
-        <v>1.0610329539459689E-8</v>
-      </c>
-      <c r="C20" s="1">
-        <f>B20*10^9</f>
-        <v>10.610329539459689</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21">
-        <f>10.7*10^6</f>
-        <v>10700000</v>
-      </c>
-      <c r="C21" s="1"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22">
-        <f>1/((2*PI()*B21)^2*B20)</f>
-        <v>2.0851813663887067E-8</v>
-      </c>
-      <c r="C22" s="1">
-        <f>B22*10^9</f>
-        <v>20.851813663887068</v>
       </c>
     </row>
   </sheetData>

--- a/lab3/mixer-oscillator/calculator.xlsx
+++ b/lab3/mixer-oscillator/calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pig\Documents\ee251\lab3\mixer-oscillator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{543B40AF-891B-491D-A4A4-6E8AE20A8D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BA922D-FBE4-4DDA-9F58-8D7F5910FAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8736" yWindow="696" windowWidth="13740" windowHeight="11232" xr2:uid="{A50CB518-3203-47F3-A69B-33C5CFC9F0B6}"/>
+    <workbookView xWindow="15984" yWindow="1404" windowWidth="12732" windowHeight="12276" xr2:uid="{A50CB518-3203-47F3-A69B-33C5CFC9F0B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -116,10 +116,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -529,13 +528,13 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5">
         <f>B5</f>
         <v>20</v>
       </c>
@@ -637,7 +636,7 @@
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <f>B10*SQRT(B12*10^(-9)/(B9*10^(-9)))</f>
         <v>327.23446243193439</v>
       </c>
